--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484269_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484269_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3448</v>
+        <v>4.874</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4078</v>
+        <v>3.5089</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9371</v>
+        <v>1.3651</v>
       </c>
       <c r="G2" t="n">
         <v>3.3786</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0947</v>
+        <v>1.6239</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0689</v>
+        <v>0.17</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0258</v>
+        <v>1.4539</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4959</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4457</v>
+        <v>3.5237</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2536</v>
+        <v>2.9502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1922</v>
+        <v>0.5735</v>
       </c>
       <c r="G3" t="n">
         <v>2.4719</v>
@@ -688,13 +688,13 @@
         <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0164</v>
+        <v>1.0943</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5147</v>
+        <v>0.2113</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5017</v>
+        <v>0.883</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4332</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9757</v>
+        <v>1.8317</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1433</v>
+        <v>1.2444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8324</v>
+        <v>0.5873</v>
       </c>
       <c r="G4" t="n">
         <v>1.3523</v>
@@ -766,13 +766,13 @@
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2094</v>
+        <v>1.0654</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.22</v>
+        <v>-0.1189</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4294</v>
+        <v>1.1843</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0611</v>
+        <v>0.2518</v>
       </c>
       <c r="E5" t="n">
         <v>-0.5557</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6169</v>
+        <v>0.8075</v>
       </c>
       <c r="G5" t="n">
         <v>0.1094</v>
@@ -844,13 +844,13 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4243</v>
+        <v>0.6149</v>
       </c>
       <c r="T5" t="n">
         <v>0.3715</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0528</v>
+        <v>0.2434</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2772</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.552</v>
+        <v>-1.9643</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2847</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8368</v>
+        <v>-2.9457</v>
       </c>
       <c r="G6" t="n">
         <v>1.3099</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8298</v>
+        <v>0.4175</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2037</v>
+        <v>-0.0997</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6261</v>
+        <v>0.5172</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1522</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3793</v>
+        <v>-2.2653</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5602</v>
+        <v>-0.7258</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-1.5395</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.839</v>
+        <v>-1.8744</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7444</v>
+        <v>1.0919</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0946</v>
+        <v>-2.9662</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1428</v>
+        <v>0.927</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1023</v>
+        <v>2.9483</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-2.0213</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9818</v>
+        <v>-2.8014</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8468</v>
+        <v>-1.8565</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.135</v>
+        <v>-0.9449</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-3.5162</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6317</v>
+        <v>0.6644</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4458</v>
+        <v>-0.187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.186</v>
+        <v>0.8514</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.8981</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5881</v>
+        <v>-2.4784</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1303</v>
+        <v>-1.8422</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4578</v>
+        <v>-0.6361</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8744</v>
+        <v>-1.6481</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0919</v>
+        <v>-1.459</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9662</v>
+        <v>-0.1891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.927</v>
+        <v>0.1244</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9483</v>
+        <v>0.0435</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0213</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8014</v>
+        <v>-1.7725</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8565</v>
+        <v>-1.5024</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9449</v>
+        <v>-0.27</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9534</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.5162</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3416</v>
+        <v>0.1231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5915</v>
+        <v>-0.0598</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9331</v>
+        <v>0.1829</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8981</v>
+        <v>0.6093</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0503</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1522</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7668</v>
+        <v>-2.7123</v>
       </c>
       <c r="E9" t="n">
         <v>-0.4913</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2754</v>
+        <v>-2.221</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2075</v>
@@ -1156,13 +1156,13 @@
         <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1453</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9724</v>
+        <v>-2.7565</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1456</v>
+        <v>-1.9647</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8268</v>
+        <v>-0.7919</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6481</v>
+        <v>-1.839</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.459</v>
+        <v>-1.7444</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1891</v>
+        <v>-0.0946</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1244</v>
+        <v>0.1428</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0435</v>
+        <v>0.1023</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7725</v>
+        <v>-1.9818</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5024</v>
+        <v>-1.8468</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.27</v>
+        <v>-0.135</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3709</v>
+        <v>0.2545</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3631</v>
+        <v>0.0413</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0077</v>
+        <v>0.2132</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9751</v>
+        <v>-2.8116</v>
       </c>
       <c r="E11" t="n">
         <v>-2.2774</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6977</v>
+        <v>-0.5342</v>
       </c>
       <c r="G11" t="n">
         <v>0.108</v>
@@ -1312,13 +1312,13 @@
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.356</v>
+        <v>-0.1926</v>
       </c>
       <c r="T11" t="n">
         <v>-0.4842</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1281</v>
+        <v>0.2916</v>
       </c>
       <c r="V11" t="n">
         <v>0.3985</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0904</v>
+        <v>-3.9893</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7335</v>
+        <v>-2.6324</v>
       </c>
       <c r="F12" t="n">
         <v>-1.3569</v>
@@ -1390,10 +1390,10 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0467</v>
+        <v>0.1479</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U12" t="n">
         <v>0.1678</v>
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4968</v>
+        <v>-8.496499999999997</v>
       </c>
       <c r="E13" t="n">
         <v>-1.804599999999999</v>
@@ -1435,7 +1435,7 @@
         <v>1.324900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6983</v>
+        <v>-0.6983000000000003</v>
       </c>
       <c r="I13" t="n">
         <v>2.0233</v>
@@ -1468,13 +1468,13 @@
         <v>14.6506</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7224</v>
+        <v>5.722500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3568000000000001</v>
+        <v>-0.3570000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>6.0794</v>
+        <v>6.079499999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-3.8234</v>
@@ -1483,7 +1483,7 @@
         <v>4.1005</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.9239</v>
+        <v>-7.923899999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9548</v>
+        <v>4.2466</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7725</v>
+        <v>1.8736</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1823</v>
+        <v>2.373</v>
       </c>
       <c r="G14" t="n">
         <v>1.9369</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4081</v>
+        <v>-1.1163</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6252</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6818</v>
+        <v>-0.4912</v>
       </c>
       <c r="V14" t="n">
         <v>0.8865</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8351</v>
+        <v>3.8415</v>
       </c>
       <c r="E15" t="n">
-        <v>4.179</v>
+        <v>4.0779</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3439</v>
+        <v>-0.2363</v>
       </c>
       <c r="G15" t="n">
         <v>-0.405</v>
@@ -1624,13 +1624,13 @@
         <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0094</v>
+        <v>0.0159</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1732</v>
+        <v>-0.2743</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1826</v>
+        <v>0.2902</v>
       </c>
       <c r="V15" t="n">
         <v>1.4959</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1465</v>
+        <v>2.4576</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3189</v>
+        <v>3.5211</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1724</v>
+        <v>-1.0635</v>
       </c>
       <c r="G16" t="n">
         <v>1.4211</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9508</v>
+        <v>-0.6397</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4842</v>
+        <v>-0.282</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4667</v>
+        <v>-0.3577</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2772</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9895</v>
+        <v>1.8727</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0582</v>
+        <v>0.1593</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9313</v>
+        <v>1.7134</v>
       </c>
       <c r="G17" t="n">
         <v>1.207</v>
@@ -1780,13 +1780,13 @@
         <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.503</v>
+        <v>-0.6197</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6252</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2233</v>
+        <v>0.0054</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2257</v>
+        <v>-0.1644</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3251</v>
+        <v>-0.2816</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0994</v>
+        <v>0.1171</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0464</v>
@@ -2014,13 +2014,13 @@
         <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>0.514</v>
+        <v>0.1239</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5614</v>
+        <v>-0.0453</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0474</v>
+        <v>0.1691</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5215</v>
+        <v>-0.3751</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1937</v>
+        <v>0.0086</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3278</v>
+        <v>-0.3836</v>
       </c>
       <c r="G21" t="n">
         <v>0.7409</v>
@@ -2092,13 +2092,13 @@
         <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3638</v>
+        <v>-0.2174</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.7056</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5441</v>
+        <v>0.4883</v>
       </c>
       <c r="V21" t="n">
         <v>0.6642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2595</v>
+        <v>-0.8759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4494</v>
+        <v>0.7528</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.709</v>
+        <v>-1.6286</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1468</v>
@@ -2170,13 +2170,13 @@
         <v>2.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6086</v>
+        <v>-0.2249</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2105</v>
+        <v>-0.9071</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6019</v>
+        <v>0.6822</v>
       </c>
       <c r="V22" t="n">
         <v>1.4959</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.747</v>
+        <v>-1.3112</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9144</v>
+        <v>-0.7964</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8326</v>
+        <v>-0.5148</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1847</v>
+        <v>-0.1504</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8205</v>
+        <v>0.6585</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3642</v>
+        <v>-0.8089</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9614</v>
+        <v>2.3763</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0018</v>
+        <v>2.3753</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>0.001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2233</v>
+        <v>-2.5267</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8186</v>
+        <v>-1.7168</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4047</v>
+        <v>-0.8099</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3907</v>
+        <v>3.1255</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4925</v>
+        <v>-0.5048</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4925</v>
+        <v>-0.8872</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.3823</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5545</v>
+        <v>-1.8279</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7572</v>
+        <v>-2.1514</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9986</v>
+        <v>-1.3188</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7585</v>
+        <v>-0.8326</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1504</v>
+        <v>-3.1847</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6585</v>
+        <v>-2.8205</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8089</v>
+        <v>-0.3642</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3763</v>
+        <v>-1.9614</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3753</v>
+        <v>-2.0018</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001</v>
+        <v>0.0405</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5267</v>
+        <v>-1.2233</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7168</v>
+        <v>-0.8186</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8099</v>
+        <v>-0.4047</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1255</v>
+        <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9508</v>
+        <v>0.0881</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0894</v>
+        <v>0.0881</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1386</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8279</v>
+        <v>0.5545</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.496500000000001</v>
+        <v>9.170500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>6.691800000000002</v>
+        <v>6.6919</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8048</v>
+        <v>2.4789</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3249</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6982000000000003</v>
+        <v>0.6982000000000004</v>
       </c>
       <c r="I25" t="n">
         <v>-2.0232</v>
@@ -2404,19 +2404,19 @@
         <v>26.3714</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.7226</v>
+        <v>-5.0483</v>
       </c>
       <c r="T25" t="n">
         <v>-6.0794</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3568000000000001</v>
+        <v>1.0308</v>
       </c>
       <c r="V25" t="n">
         <v>3.823599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>7.924</v>
+        <v>7.923999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-4.1006</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484269_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484269_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.4332</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2518</v>
+        <v>1.521</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5557</v>
+        <v>1.521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8075</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1094</v>
+        <v>1.521</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6055</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.715</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0495</v>
+        <v>1.521</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5308</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5803</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0599</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6149</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3715</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2434</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9643</v>
+        <v>0.2518</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9814000000000001</v>
+        <v>-0.5557</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9457</v>
+        <v>0.8075</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3099</v>
+        <v>0.1094</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1601</v>
+        <v>-0.6055</v>
       </c>
       <c r="I6" t="n">
-        <v>1.47</v>
+        <v>0.715</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5153</v>
+        <v>0.0495</v>
       </c>
       <c r="K6" t="n">
-        <v>1.966</v>
+        <v>-0.5308</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5493</v>
+        <v>0.5803</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2055</v>
+        <v>0.0599</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1261</v>
+        <v>-0.0747</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0793</v>
+        <v>0.1346</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5395</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.7115</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4175</v>
+        <v>0.6149</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0997</v>
+        <v>0.3715</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5172</v>
+        <v>0.2434</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1522</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4294</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2653</v>
+        <v>-1.9643</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7258</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5395</v>
+        <v>-2.9457</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8744</v>
+        <v>1.3099</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0919</v>
+        <v>-0.1601</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9662</v>
+        <v>1.47</v>
       </c>
       <c r="J7" t="n">
-        <v>0.927</v>
+        <v>4.5153</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9483</v>
+        <v>1.966</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0213</v>
+        <v>2.5493</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8014</v>
+        <v>-3.2055</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8565</v>
+        <v>-2.1261</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9449</v>
+        <v>-1.0793</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9534</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.5162</v>
+        <v>-3.7115</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6644</v>
+        <v>0.4175</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.187</v>
+        <v>-0.0997</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8514</v>
+        <v>0.5172</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8981</v>
+        <v>-1.1522</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0503</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1522</v>
+        <v>-1.4294</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4784</v>
+        <v>-2.2653</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8422</v>
+        <v>-0.7258</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6361</v>
+        <v>-1.5395</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6481</v>
+        <v>-1.8744</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.459</v>
+        <v>1.0919</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1891</v>
+        <v>-2.9662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1244</v>
+        <v>0.927</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0435</v>
+        <v>2.9483</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>-2.0213</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7725</v>
+        <v>-2.8014</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5024</v>
+        <v>-1.8565</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.27</v>
+        <v>-0.9449</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>-3.5162</v>
       </c>
       <c r="R8" t="n">
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1231</v>
+        <v>0.6644</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0598</v>
+        <v>-0.187</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1829</v>
+        <v>0.8514</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6093</v>
+        <v>0.8981</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>2.0503</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6093</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7123</v>
+        <v>-2.4784</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4913</v>
+        <v>-1.8422</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.221</v>
+        <v>-0.6361</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2075</v>
+        <v>-1.6481</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.614</v>
+        <v>-1.459</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5936</v>
+        <v>-0.1891</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0809</v>
+        <v>0.1244</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="L9" t="n">
         <v>0.0809</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2885</v>
+        <v>-1.7725</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.614</v>
+        <v>-1.5024</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6745</v>
+        <v>-0.27</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3907</v>
+        <v>-3.1255</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.1231</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1816</v>
+        <v>-0.0598</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.1829</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7565</v>
+        <v>-2.7123</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9647</v>
+        <v>-0.4913</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7919</v>
+        <v>-2.221</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.839</v>
+        <v>-1.2075</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7444</v>
+        <v>-0.614</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0946</v>
+        <v>-0.5936</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1428</v>
+        <v>0.0809</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1023</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9818</v>
+        <v>-1.2885</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8468</v>
+        <v>-0.614</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.135</v>
+        <v>-0.6745</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2545</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0413</v>
+        <v>-0.1816</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2132</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1317,72 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8116</v>
+        <v>-2.7565</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2774</v>
+        <v>-1.9647</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5342</v>
+        <v>-0.7919</v>
       </c>
       <c r="G11" t="n">
-        <v>0.108</v>
+        <v>-1.839</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5393</v>
+        <v>-1.7444</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6473</v>
+        <v>-0.0946</v>
       </c>
       <c r="J11" t="n">
-        <v>1.481</v>
+        <v>0.1428</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6984</v>
+        <v>0.1023</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7827</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3731</v>
+        <v>-1.9818</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2377</v>
+        <v>-1.8468</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1354</v>
+        <v>-0.135</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.4929</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1926</v>
+        <v>0.2545</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4842</v>
+        <v>0.0413</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2916</v>
+        <v>0.2132</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3985</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8201000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1407,11 +1462,16 @@
       <c r="X12" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.496499999999997</v>
+        <v>-4.3326</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.804599999999999</v>
+        <v>-3.7984</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.6919</v>
+        <v>-0.5342</v>
       </c>
       <c r="G13" t="n">
-        <v>1.324900000000001</v>
+        <v>-1.413</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6983000000000003</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0233</v>
+        <v>-0.5667</v>
       </c>
       <c r="J13" t="n">
-        <v>20.8227</v>
+        <v>-0.0399</v>
       </c>
       <c r="K13" t="n">
-        <v>14.7481</v>
+        <v>0.3914</v>
       </c>
       <c r="L13" t="n">
-        <v>6.0748</v>
+        <v>-0.4313</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.4981</v>
+        <v>-1.3731</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.4465</v>
+        <v>-1.2377</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.0514</v>
+        <v>-0.1354</v>
       </c>
       <c r="P13" t="n">
-        <v>-11.7205</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q13" t="n">
-        <v>-26.3713</v>
+        <v>-4.4929</v>
       </c>
       <c r="R13" t="n">
-        <v>14.6506</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>5.722500000000001</v>
+        <v>-0.1926</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3570000000000001</v>
+        <v>-0.4842</v>
       </c>
       <c r="U13" t="n">
-        <v>6.079499999999999</v>
+        <v>0.2916</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.8234</v>
+        <v>0.3985</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1005</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.923899999999999</v>
+        <v>-0.8201000000000001</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>CB ANDRATX</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2466</v>
+        <v>-8.496500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8736</v>
+        <v>-1.804600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.373</v>
+        <v>-6.6919</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9369</v>
+        <v>1.3249</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9112</v>
+        <v>-0.6982999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0257</v>
+        <v>2.0233</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6122</v>
+        <v>20.8228</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1256</v>
+        <v>14.7481</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4866</v>
+        <v>6.074799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3247</v>
+        <v>-19.4981</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2144</v>
+        <v>-15.4465</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5391</v>
+        <v>-4.0514</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5395</v>
+        <v>-11.7205</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-26.3713</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>14.6506</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1163</v>
+        <v>5.722500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6252</v>
+        <v>-0.357</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4912</v>
+        <v>6.079499999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>-3.8234</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>4.1005</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.923899999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8415</v>
+        <v>4.2466</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0779</v>
+        <v>1.8736</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2363</v>
+        <v>2.373</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.405</v>
+        <v>1.9369</v>
       </c>
       <c r="H15" t="n">
-        <v>0.715</v>
+        <v>0.9112</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.12</v>
+        <v>1.0257</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8564</v>
+        <v>1.6122</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0875</v>
+        <v>1.1256</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7688</v>
+        <v>0.4866</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.2613</v>
+        <v>0.3247</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3725</v>
+        <v>-0.2144</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8889</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0159</v>
+        <v>-1.1163</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2743</v>
+        <v>-0.6252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2902</v>
+        <v>-0.4912</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4959</v>
+        <v>0.8865</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4576</v>
+        <v>3.8415</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5211</v>
+        <v>4.0779</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0635</v>
+        <v>-0.2363</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4211</v>
+        <v>-0.405</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4073</v>
+        <v>0.715</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0138</v>
+        <v>-1.12</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1938</v>
+        <v>2.8564</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6401</v>
+        <v>2.0875</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5537</v>
+        <v>0.7688</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7727</v>
+        <v>-3.2613</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2328</v>
+        <v>-1.3725</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5399</v>
+        <v>-1.8889</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6397</v>
+        <v>0.0159</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.282</v>
+        <v>-0.2743</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3577</v>
+        <v>0.2902</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8727</v>
+        <v>2.4576</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1593</v>
+        <v>3.5211</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7134</v>
+        <v>-1.0635</v>
       </c>
       <c r="G17" t="n">
-        <v>1.207</v>
+        <v>1.4211</v>
       </c>
       <c r="H17" t="n">
-        <v>1.086</v>
+        <v>1.4073</v>
       </c>
       <c r="I17" t="n">
-        <v>0.121</v>
+        <v>0.0138</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7612</v>
+        <v>3.1938</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6398</v>
+        <v>2.6401</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>0.5537</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5542</v>
+        <v>-1.7727</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5538</v>
+        <v>-1.2328</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0004</v>
+        <v>-0.5399</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6197</v>
+        <v>-0.6397</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6252</v>
+        <v>-0.282</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0054</v>
+        <v>-0.3577</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1894,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9226</v>
+        <v>1.8727</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4447</v>
+        <v>0.1593</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3674</v>
+        <v>1.7134</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3914</v>
+        <v>1.207</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0397</v>
+        <v>1.086</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4311</v>
+        <v>0.121</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4947</v>
+        <v>1.7612</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3328</v>
+        <v>1.6398</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1619</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1032</v>
+        <v>-0.5542</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3725</v>
+        <v>-0.5538</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2692</v>
+        <v>-0.0004</v>
       </c>
       <c r="P18" t="n">
         <v>1.5627</v>
@@ -1858,28 +1939,33 @@
         <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9767</v>
+        <v>-0.6197</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0689</v>
+        <v>0.0054</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0549</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,46 +1977,46 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7075</v>
+        <v>0.9226</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8599</v>
+        <v>-0.4447</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5674</v>
+        <v>1.3674</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9111</v>
+        <v>0.3914</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1829</v>
+        <v>-0.0397</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7282</v>
+        <v>0.4311</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8143</v>
+        <v>1.4947</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7601</v>
+        <v>1.3328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0543</v>
+        <v>0.1619</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9032</v>
+        <v>-1.1032</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5771</v>
+        <v>-1.3725</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.2692</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
         <v>2.5395</v>
@@ -1945,19 +2031,24 @@
         <v>-0.0689</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1638</v>
+        <v>-0.0549</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1638</v>
+        <v>-0.0549</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1644</v>
+        <v>0.7075</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2816</v>
+        <v>-0.8599</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1171</v>
+        <v>1.5674</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0464</v>
+        <v>0.9111</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7994</v>
+        <v>0.1829</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8458</v>
+        <v>0.7282</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7403999999999999</v>
+        <v>1.8143</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9672</v>
+        <v>1.7601</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2268</v>
+        <v>0.0543</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7868</v>
+        <v>-0.9032</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1678</v>
+        <v>-1.5771</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.619</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S20" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.7348</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.1239</v>
-      </c>
       <c r="T20" t="n">
-        <v>-0.0453</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1691</v>
+        <v>-0.0689</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3751</v>
+        <v>-0.1644</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0086</v>
+        <v>-0.2816</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3836</v>
+        <v>0.1171</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7409</v>
+        <v>-2.0464</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0806</v>
+        <v>0.7994</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6603</v>
+        <v>-2.8458</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4024</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>2.067</v>
+        <v>1.9672</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3354</v>
+        <v>-1.2268</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6615</v>
+        <v>-2.7868</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9864</v>
+        <v>-1.1678</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6751</v>
+        <v>-1.619</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2174</v>
+        <v>0.1239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7056</v>
+        <v>-0.0453</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4883</v>
+        <v>0.1691</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8759</v>
+        <v>-0.3751</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7528</v>
+        <v>0.0086</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6286</v>
+        <v>-0.3836</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1468</v>
+        <v>0.7409</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2825</v>
+        <v>0.0806</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1356</v>
+        <v>0.6603</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2076</v>
+        <v>3.4024</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4528</v>
+        <v>2.067</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7548</v>
+        <v>1.3354</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.3545</v>
+        <v>-2.6615</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.7352</v>
+        <v>-1.9864</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6192</v>
+        <v>-0.6751</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9301</v>
+        <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2249</v>
+        <v>-0.2174</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9071</v>
+        <v>-0.7056</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6822</v>
+        <v>0.4883</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4959</v>
+        <v>0.6642</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3824</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8865</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3112</v>
+        <v>-0.8759</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7964</v>
+        <v>0.7528</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5148</v>
+        <v>-1.6286</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1504</v>
+        <v>-2.1468</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6585</v>
+        <v>-2.2825</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8089</v>
+        <v>0.1356</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3763</v>
+        <v>2.2076</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3753</v>
+        <v>0.4528</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001</v>
+        <v>1.7548</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5267</v>
+        <v>-4.3545</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7168</v>
+        <v>-2.7352</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8099</v>
+        <v>-1.6192</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1255</v>
+        <v>2.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5048</v>
+        <v>-0.2249</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8872</v>
+        <v>-0.9071</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3823</v>
+        <v>0.6822</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8279</v>
+        <v>1.4959</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3321</v>
+        <v>2.3824</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1514</v>
+        <v>-1.3112</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3188</v>
+        <v>-0.7964</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8326</v>
+        <v>-0.5148</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1847</v>
+        <v>-0.1504</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8205</v>
+        <v>0.6585</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3642</v>
+        <v>-0.8089</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9614</v>
+        <v>2.3763</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0018</v>
+        <v>2.3753</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0405</v>
+        <v>0.001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2233</v>
+        <v>-2.5267</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8186</v>
+        <v>-1.7168</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4047</v>
+        <v>-0.8099</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3907</v>
+        <v>3.1255</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0881</v>
+        <v>-0.5048</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0881</v>
+        <v>-0.8872</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.3823</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5545</v>
+        <v>-1.8279</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-2.1514</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.3188</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.8326</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.1847</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.8205</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.3642</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.9614</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.0018</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.2233</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.8186</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484269_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>9.170500000000001</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>6.6919</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>2.4789</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-1.3249</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>0.6982000000000004</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-2.0232</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>19.4979</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>15.4464</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>4.0516</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-20.8227</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-14.7479</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-6.0749</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>11.7206</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-14.6506</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>26.3714</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>-5.0483</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-6.0794</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1.0308</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>3.823599999999999</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>7.923999999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-4.1006</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
